--- a/oportunidad-generar-core-main/data/output/CORE_PC_20250256445_test.xlsx
+++ b/oportunidad-generar-core-main/data/output/CORE_PC_20250256445_test.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aortega\.nuget\packages\oportunidad-generar-core-main\1.0.30-e03\content\data\output\test\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aortega\.nuget\packages\oportunidad-generar-core-main\1.0.26-e04\content\data\output\test\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA71BC5B-6F67-4A89-955E-094287E0BDAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C10F7E0-AB9B-447F-A96E-6EA3AB75CADB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="17520" tabRatio="740" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/oportunidad-generar-core-main/data/output/CORE_PC_20250256445_test.xlsx
+++ b/oportunidad-generar-core-main/data/output/CORE_PC_20250256445_test.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aortega\.nuget\packages\oportunidad-generar-core-main\1.0.26-e04\content\data\output\test\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aortega\.nuget\packages\oportunidad-generar-core-main\1.0.28-e05\content\data\output\test\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C10F7E0-AB9B-447F-A96E-6EA3AB75CADB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74EEE37C-CA16-40E4-B1B4-EAA0E505A6D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="17520" tabRatio="740" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/oportunidad-generar-core-main/data/output/CORE_PC_20250256445_test.xlsx
+++ b/oportunidad-generar-core-main/data/output/CORE_PC_20250256445_test.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aortega\.nuget\packages\oportunidad-generar-core-main\1.0.28-e05\content\data\output\test\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aortega\.nuget\packages\oportunidad-generar-core-main\1.0.29-e06\content\data\output\test\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74EEE37C-CA16-40E4-B1B4-EAA0E505A6D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FDEB4DB8-BE42-4035-892F-80121DDDA4F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="17520" tabRatio="740" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
